--- a/KURIKULUM2026_REVISI/019_AUDIT_KRITIS_KESELARASAN_FOLDER_REVISI_23082026_212923.xlsx
+++ b/KURIKULUM2026_REVISI/019_AUDIT_KRITIS_KESELARASAN_FOLDER_REVISI_23082026_212923.xlsx
@@ -830,7 +830,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Konsistensi SKS `STI-625` Smart City</t>
+          <t>Konsistensi SKS `STI-727` Smart City</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -3070,7 +3070,7 @@
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>P0-3c. Akar Penyebab: `STI-625` Smart City Tercatat 3 SKS</t>
+          <t>P0-3c. Akar Penyebab: `STI-727` Smart City Tercatat 3 SKS</t>
         </is>
       </c>
       <c r="B152" s="4" t="n"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>`• STI-625 Smart City (3)`</t>
+          <t>`• STI-727 Smart City (3)`</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>`STI-624` Integrasi Layanan Cerdas AI</t>
+          <t>`STI-726` Integrasi Layanan Cerdas AI</t>
         </is>
       </c>
       <c r="C219" s="8" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>`STI-627`, `MKU-204`</t>
+          <t>`STI-727`, `MKU-204`</t>
         </is>
       </c>
       <c r="E220" s="10" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>`STI-625` Smart City</t>
+          <t>`STI-727` Smart City</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B379" s="8" t="inlineStr">
         <is>
-          <t>Sheet 9 (`STI-624`)</t>
+          <t>Sheet 9 (`STI-726`)</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B382" s="10" t="inlineStr">
         <is>
-          <t>Sheet 12 (`STI-626`)</t>
+          <t>Sheet 12 (`STI-726`)</t>
         </is>
       </c>
       <c r="C382" s="9" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="B604" s="8" t="inlineStr">
         <is>
-          <t>**64/65 benar**; hanya `STI-625` yang salah SKS (semesternya benar) ✅</t>
+          <t>**64/65 benar**; hanya `STI-727` yang salah SKS (semesternya benar) ✅</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="B648" s="10" t="inlineStr">
         <is>
-          <t>Koreksi angka P0-3 di Buku Final (komposisi rumpun, Sem 6, kumulatif Sem 6–7, `STI-625`)</t>
+          <t>Koreksi angka P0-3 di Buku Final (komposisi rumpun, Sem 6, kumulatif Sem 6–7, `STI-727`)</t>
         </is>
       </c>
       <c r="C648" s="10" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="B691" s="10" t="inlineStr">
         <is>
-          <t>P0-3c (`STI-625` 3 SKS)</t>
+          <t>P0-3c (`STI-727` 3 SKS)</t>
         </is>
       </c>
       <c r="C691" s="9" t="inlineStr">
